--- a/case-study/metrics_without_rubric.xlsx
+++ b/case-study/metrics_without_rubric.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\Desktop\Proyectos Investigación\08_Correcion examenes - SoftwareX\Revision 2\Calculo de metricas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\Desktop\Proyectos Investigación\08_Correcion examenes - SoftwareX\Repositorio GitHub\EvaluAI-Project-main\case-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79BA6E7-5997-4224-AE9D-2E0ACF4C0A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F29669-CF76-4B59-8646-4F48CABF387C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6807" yWindow="2319" windowWidth="26930" windowHeight="14419" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5529" yWindow="177" windowWidth="23543" windowHeight="11098" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paired data" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="ICC" sheetId="3" r:id="rId3"/>
     <sheet name="Confidence Intervals" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>AI vs. Human grading – paired cases (no-rubric condition)</t>
   </si>
@@ -324,6 +321,27 @@
   </si>
   <si>
     <t>Error-metric CIs: t-based intervals across the 13 paired submissions. ICC(2,1) CI: F-distribution-based interval using the existing two-way ANOVA components.</t>
+  </si>
+  <si>
+    <t>SD (STDEV.S) across the three AI total-score runs for each paired submission.</t>
+  </si>
+  <si>
+    <t>SD total (0–6)</t>
+  </si>
+  <si>
+    <t>SD normalized (0–1)</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Mean SD total (0–6)</t>
+  </si>
+  <si>
+    <t>Mean SD normalized (0–1)</t>
+  </si>
+  <si>
+    <t>Paired submissions (n)</t>
   </si>
 </sst>
 </file>
@@ -335,7 +353,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -345,12 +363,14 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -371,8 +391,28 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,8 +431,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -400,11 +446,131 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -428,18 +594,44 @@
     <xf numFmtId="166" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -951,94 +1143,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Paired data"/>
-      <sheetName val="Metrics"/>
-      <sheetName val="ICC"/>
-      <sheetName val="Confidence Intervals"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="A4">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>14</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -1235,64 +1339,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="15.08203125" customWidth="1"/>
+    <col min="18" max="18" width="15.125" customWidth="1"/>
     <col min="19" max="19" width="13.25" customWidth="1"/>
     <col min="20" max="20" width="16.25" customWidth="1"/>
-    <col min="21" max="21" width="17.58203125" customWidth="1"/>
-    <col min="22" max="22" width="12.6640625" customWidth="1"/>
+    <col min="21" max="21" width="17.625" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
     <col min="23" max="23" width="12.25" customWidth="1"/>
     <col min="24" max="24" width="12.75" customWidth="1"/>
     <col min="25" max="25" width="13" customWidth="1"/>
-    <col min="26" max="26" width="14.08203125" customWidth="1"/>
-    <col min="27" max="27" width="13.1640625" customWidth="1"/>
+    <col min="26" max="26" width="14.125" customWidth="1"/>
+    <col min="27" max="27" width="13.125" customWidth="1"/>
     <col min="28" max="28" width="14.25" customWidth="1"/>
     <col min="29" max="29" width="14" customWidth="1"/>
     <col min="30" max="30" width="12.5" customWidth="1"/>
-    <col min="31" max="31" width="12.83203125" customWidth="1"/>
+    <col min="31" max="31" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-    </row>
-    <row r="3" spans="1:33" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+    </row>
+    <row r="3" spans="1:33" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +1497,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1516,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1639,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1756,7 +1860,7 @@
         <v>0.1388888888888889</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1873,7 +1977,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1990,7 +2094,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2107,7 +2211,7 @@
         <v>0.28888888888888892</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2224,7 +2328,7 @@
         <v>0.86111111111111116</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -2341,7 +2445,7 @@
         <v>0.4055555555555555</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -2458,7 +2562,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2575,7 +2679,7 @@
         <v>0.34722222222222227</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2692,7 +2796,7 @@
         <v>0.59444444444444444</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2809,7 +2913,7 @@
         <v>0.4777777777777778</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2926,7 +3030,7 @@
         <v>0.72500000000000009</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2945,26 +3049,26 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2978,23 +3082,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="20.375" customWidth="1"/>
+    <col min="11" max="11" width="24.75" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="G1" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:12" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
@@ -3010,8 +3131,23 @@
       <c r="E3" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -3030,8 +3166,27 @@
         <f>SQRT(D4)</f>
         <v>0.40625452002745149</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G4" s="20">
+        <f>'Paired data'!A4</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V4:X4)</f>
+        <v>0.28867513459481275</v>
+      </c>
+      <c r="I4" s="22">
+        <f t="shared" ref="I4:I16" si="0">H4/6</f>
+        <v>4.8112522432468795E-2</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="L4" s="22">
+        <f>AVERAGE(H4:H16)</f>
+        <v>0.2677489360943956</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -3050,8 +3205,27 @@
         <f>SQRT(D5)</f>
         <v>0.88979254280465236</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G5" s="20">
+        <f>'Paired data'!A5</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V5:X5)</f>
+        <v>2.7194799110210365E-16</v>
+      </c>
+      <c r="I5" s="22">
+        <f t="shared" si="0"/>
+        <v>4.5324665183683939E-17</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="25">
+        <f>AVERAGE(I4:I16)</f>
+        <v>4.4624822682399271E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -3070,8 +3244,27 @@
         <f>E4/3</f>
         <v>0.13541817334248382</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G6" s="20">
+        <f>'Paired data'!A6</f>
+        <v>3</v>
+      </c>
+      <c r="H6" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V6:X6)</f>
+        <v>0.28867513459481275</v>
+      </c>
+      <c r="I6" s="22">
+        <f t="shared" si="0"/>
+        <v>4.8112522432468795E-2</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="27">
+        <f>COUNT(G4:G16)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -3090,15 +3283,67 @@
         <f>E5/3</f>
         <v>0.29659751426821745</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G7" s="20">
+        <f>'Paired data'!A7</f>
+        <v>4</v>
+      </c>
+      <c r="H7" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V7:X7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G8" s="20">
+        <f>'Paired data'!A8</f>
+        <v>5</v>
+      </c>
+      <c r="H8" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V8:X8)</f>
+        <v>0.22912878474779211</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="0"/>
+        <v>3.8188130791298687E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="G9" s="20">
+        <f>'Paired data'!A9</f>
+        <v>7</v>
+      </c>
+      <c r="H9" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V9:X9)</f>
+        <v>0.2516611478423586</v>
+      </c>
+      <c r="I9" s="22">
+        <f t="shared" si="0"/>
+        <v>4.1943524640393103E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G10" s="20">
+        <f>'Paired data'!A10</f>
+        <v>8</v>
+      </c>
+      <c r="H10" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V10:X10)</f>
+        <v>0.30550504633038922</v>
+      </c>
+      <c r="I10" s="22">
+        <f t="shared" si="0"/>
+        <v>5.0917507721731536E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -3117,8 +3362,20 @@
         <f>SQRT(D11)</f>
         <v>0.93677250976036586</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G11" s="20">
+        <f>'Paired data'!A11</f>
+        <v>9</v>
+      </c>
+      <c r="H11" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V11:X11)</f>
+        <v>0.27537852736430518</v>
+      </c>
+      <c r="I11" s="22">
+        <f t="shared" si="0"/>
+        <v>4.5896421227384195E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -3137,11 +3394,81 @@
         <f>E11/6</f>
         <v>0.15612875162672765</v>
       </c>
+      <c r="G12" s="20">
+        <f>'Paired data'!A12</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V12:X12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G13" s="20">
+        <f>'Paired data'!A13</f>
+        <v>11</v>
+      </c>
+      <c r="H13" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V13:X13)</f>
+        <v>1.282900359861721</v>
+      </c>
+      <c r="I13" s="22">
+        <f t="shared" si="0"/>
+        <v>0.21381672664362017</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G14" s="20">
+        <f>'Paired data'!A14</f>
+        <v>12</v>
+      </c>
+      <c r="H14" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V14:X14)</f>
+        <v>0.11547005383792526</v>
+      </c>
+      <c r="I14" s="22">
+        <f t="shared" si="0"/>
+        <v>1.9245008972987542E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G15" s="20">
+        <f>'Paired data'!A15</f>
+        <v>13</v>
+      </c>
+      <c r="H15" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V15:X15)</f>
+        <v>0.11547005383792526</v>
+      </c>
+      <c r="I15" s="22">
+        <f t="shared" si="0"/>
+        <v>1.9245008972987542E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G16" s="20">
+        <f>'Paired data'!A16</f>
+        <v>14</v>
+      </c>
+      <c r="H16" s="21">
+        <f>_xlfn.STDEV.S('Paired data'!V16:X16)</f>
+        <v>0.3278719262151002</v>
+      </c>
+      <c r="I16" s="28">
+        <f t="shared" si="0"/>
+        <v>5.4645321035850035E-2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:E9"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3150,7 +3477,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="12" width="14" customWidth="1"/>
@@ -3158,40 +3485,40 @@
     <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-    </row>
-    <row r="2" spans="1:14" ht="32.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+    </row>
+    <row r="2" spans="1:14" ht="32.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-    </row>
-    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="4" spans="1:14" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
@@ -3235,7 +3562,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>'Paired data'!A4</f>
         <v>1</v>
@@ -3291,7 +3618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>'Paired data'!A5</f>
         <v>2</v>
@@ -3347,7 +3674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>'Paired data'!A6</f>
         <v>3</v>
@@ -3404,7 +3731,7 @@
         <v>5.3708867521367525</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>'Paired data'!A7</f>
         <v>4</v>
@@ -3461,7 +3788,7 @@
         <v>0.36929487179487186</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>'Paired data'!A8</f>
         <v>5</v>
@@ -3518,7 +3845,7 @@
         <v>0.15519764957264956</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>'Paired data'!A9</f>
         <v>7</v>
@@ -3575,7 +3902,7 @@
         <v>0.91013297165788121</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>'Paired data'!A10</f>
         <v>8</v>
@@ -3631,7 +3958,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>'Paired data'!A11</f>
         <v>9</v>
@@ -3681,7 +4008,7 @@
         <v>2.0134779750164223E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>'Paired data'!A12</f>
         <v>10</v>
@@ -3731,7 +4058,7 @@
         <v>0.22868014464168276</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>'Paired data'!A13</f>
         <v>11</v>
@@ -3781,7 +4108,7 @@
         <v>0.15592373438527243</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>'Paired data'!A14</f>
         <v>12</v>
@@ -3831,7 +4158,7 @@
         <v>1.1847485207100594</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>'Paired data'!A15</f>
         <v>13</v>
@@ -3881,7 +4208,7 @@
         <v>0.15090236686390562</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>'Paired data'!A16</f>
         <v>14</v>
@@ -3931,7 +4258,7 @@
         <v>3.5036160420775837</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>50</v>
       </c>
@@ -3948,7 +4275,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B21">
         <f>AVERAGE(B5:B17)</f>
         <v>2.3384615384615381</v>
@@ -3978,7 +4305,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA2F830-3781-409D-82CA-D5FF011145F9}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -3990,34 +4317,34 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-    </row>
-    <row r="3" spans="1:11" ht="26.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
@@ -4046,9 +4373,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f>'[1]Paired data'!A4</f>
+        <f>'Paired data'!A4</f>
         <v>1</v>
       </c>
       <c r="B6" s="8">
@@ -4067,11 +4394,11 @@
         <v>0.11047008547008545</v>
       </c>
       <c r="G6" s="4">
-        <f>MAX(0,F6-K9*_xlfn.SINGLE(_xlfn.STDEV.S(B6:B18))/SQRT(K6))</f>
+        <f>MAX(0,F6-K9*_xlfn.STDEV.S(B6:B18)/SQRT(K6))</f>
         <v>4.1076386740595452E-2</v>
       </c>
       <c r="H6" s="4">
-        <f>F6+K9*_xlfn.SINGLE(_xlfn.STDEV.S(B6:B18))/SQRT(K6)</f>
+        <f>F6+K9*_xlfn.STDEV.S(B6:B18)/SQRT(K6)</f>
         <v>0.17986378419957544</v>
       </c>
       <c r="J6" t="s">
@@ -4082,9 +4409,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f>'[1]Paired data'!A5</f>
+        <f>'Paired data'!A5</f>
         <v>2</v>
       </c>
       <c r="B7" s="8">
@@ -4103,11 +4430,11 @@
         <v>2.4376187084520409E-2</v>
       </c>
       <c r="G7" s="4">
-        <f>MAX(0,F7-K9*_xlfn.SINGLE(_xlfn.STDEV.S(C6:C18))/SQRT(K6))</f>
+        <f>MAX(0,F7-K9*_xlfn.STDEV.S(C6:C18)/SQRT(K6))</f>
         <v>2.1659958213752842E-3</v>
       </c>
       <c r="H7" s="4">
-        <f>F7+K9*_xlfn.SINGLE(_xlfn.STDEV.S(C6:C18))/SQRT(K6)</f>
+        <f>F7+K9*_xlfn.STDEV.S(C6:C18)/SQRT(K6)</f>
         <v>4.6586378347665533E-2</v>
       </c>
       <c r="J7" t="s">
@@ -4118,9 +4445,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f>'[1]Paired data'!A6</f>
+        <f>'Paired data'!A6</f>
         <v>3</v>
       </c>
       <c r="B8" s="8">
@@ -4153,9 +4480,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f>'[1]Paired data'!A7</f>
+        <f>'Paired data'!A7</f>
         <v>4</v>
       </c>
       <c r="B9" s="8">
@@ -4173,9 +4500,9 @@
         <v>2.1788128296672284</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f>'[1]Paired data'!A8</f>
+        <f>'Paired data'!A8</f>
         <v>5</v>
       </c>
       <c r="B10" s="8">
@@ -4188,9 +4515,9 @@
       </c>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f>'[1]Paired data'!A9</f>
+        <f>'Paired data'!A9</f>
         <v>7</v>
       </c>
       <c r="B11" s="8">
@@ -4220,9 +4547,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f>'[1]Paired data'!A10</f>
+        <f>'Paired data'!A10</f>
         <v>8</v>
       </c>
       <c r="B12" s="8">
@@ -4256,9 +4583,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f>'[1]Paired data'!A11</f>
+        <f>'Paired data'!A11</f>
         <v>9</v>
       </c>
       <c r="B13" s="8">
@@ -4277,9 +4604,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f>'[1]Paired data'!A12</f>
+        <f>'Paired data'!A12</f>
         <v>10</v>
       </c>
       <c r="B14" s="8">
@@ -4298,9 +4625,9 @@
         <v>5.3708867521367525</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f>'[1]Paired data'!A13</f>
+        <f>'Paired data'!A13</f>
         <v>11</v>
       </c>
       <c r="B15" s="8">
@@ -4319,9 +4646,9 @@
         <v>0.36929487179487186</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f>'[1]Paired data'!A14</f>
+        <f>'Paired data'!A14</f>
         <v>12</v>
       </c>
       <c r="B16" s="8">
@@ -4340,9 +4667,9 @@
         <v>0.15519764957264956</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f>'[1]Paired data'!A15</f>
+        <f>'Paired data'!A15</f>
         <v>13</v>
       </c>
       <c r="B17" s="8">
@@ -4361,9 +4688,9 @@
         <v>2.3795133032733289</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f>'[1]Paired data'!A16</f>
+        <f>'Paired data'!A16</f>
         <v>14</v>
       </c>
       <c r="B18" s="8">
@@ -4382,7 +4709,7 @@
         <v>23.661327089666806</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
         <v>90</v>
       </c>
@@ -4391,7 +4718,7 @@
         <v>2.5699413670146578</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>91</v>
       </c>
@@ -4400,17 +4727,17 @@
         <v>3.0305763202630671</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="33.700000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:11" ht="33.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="J21" t="s">
         <v>48</v>
       </c>
